--- a/MiniTemplate/Datas/fishRod.xlsx
+++ b/MiniTemplate/Datas/fishRod.xlsx
@@ -676,7 +676,7 @@
           <t>捕鱼进度下降速度</t>
         </is>
       </c>
-      <c r="K4" s="1" t="inlineStr">
+      <c r="K4" s="0" t="inlineStr">
         <is>
           <t>遇到宝藏的概率</t>
         </is>
@@ -922,7 +922,7 @@
       <c r="J10" s="0" t="n">
         <v>0.15</v>
       </c>
-      <c r="K10" s="1" t="n">
+      <c r="K10" s="0" t="n">
         <v>0.08</v>
       </c>
       <c r="L10" s="0" t="n">
